--- a/rehab_expenses.xlsx
+++ b/rehab_expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\New House\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8352A18F-870C-481D-91FB-CE4B4EDD54F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8773E4F-E6C1-4588-AC83-A1B38C7990D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="713" xr2:uid="{AB74FC30-BEBC-4B99-9425-710997B15428}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="289">
   <si>
     <t>مصروفات البيت</t>
   </si>
@@ -1051,9 +1051,6 @@
   </si>
   <si>
     <t>مواد عامة من الصفار</t>
-  </si>
-  <si>
-    <t>Test - Please remove</t>
   </si>
 </sst>
 </file>
@@ -3367,8 +3364,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}" name="Table1" displayName="Table1" ref="A4:M139" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
-  <autoFilter ref="A4:M139" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}" name="Table1" displayName="Table1" ref="A4:M138" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+  <autoFilter ref="A4:M138" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{07A54FC1-E751-434C-8E2B-321DF3B580E1}" name="التاريخ" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{402B6DF9-6739-4D62-9596-2B3A39BA29DE}" name="الوصف" dataDxfId="62"/>
@@ -3790,7 +3787,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B03AB583-00B0-4E1F-8550-C73216860618}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:M148"/>
+  <dimension ref="A2:M147"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" style="22" bestFit="1" customWidth="1"/>
@@ -8178,45 +8175,19 @@
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="69">
-        <v>46188</v>
-      </c>
-      <c r="B113" s="70" t="s">
-        <v>289</v>
-      </c>
-      <c r="C113" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="D113" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="F113" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="G113" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="H113" s="71" t="s">
-        <v>52</v>
-      </c>
-      <c r="I113" s="72">
-        <v>1000000</v>
-      </c>
-      <c r="J113" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="K113" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="L113" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="M113" s="71" t="s">
-        <v>10</v>
-      </c>
+      <c r="A113" s="69"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
+      <c r="G113" s="57"/>
+      <c r="H113" s="71"/>
+      <c r="I113" s="72"/>
+      <c r="J113" s="71"/>
+      <c r="K113" s="57"/>
+      <c r="L113" s="71"/>
+      <c r="M113" s="71"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="69"/>
@@ -8240,35 +8211,53 @@
       <c r="D115" s="71"/>
       <c r="E115" s="71"/>
       <c r="F115" s="71"/>
-      <c r="G115" s="57"/>
+      <c r="G115" s="71"/>
       <c r="H115" s="71"/>
       <c r="I115" s="72"/>
       <c r="J115" s="71"/>
-      <c r="K115" s="57"/>
+      <c r="K115" s="71"/>
       <c r="L115" s="71"/>
       <c r="M115" s="71"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="69"/>
-      <c r="B116" s="70"/>
-      <c r="C116" s="71"/>
-      <c r="D116" s="71"/>
-      <c r="E116" s="71"/>
-      <c r="F116" s="71"/>
-      <c r="G116" s="71"/>
-      <c r="H116" s="71"/>
-      <c r="I116" s="72"/>
-      <c r="J116" s="71"/>
-      <c r="K116" s="71"/>
-      <c r="L116" s="71"/>
-      <c r="M116" s="71"/>
+    <row r="116" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B116" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C116" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D116" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E116" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F116" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="G116" s="29"/>
+      <c r="H116" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I116" s="30">
+        <v>20700</v>
+      </c>
+      <c r="J116" s="29"/>
+      <c r="K116" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="L116" s="29"/>
+      <c r="M116" s="29"/>
     </row>
     <row r="117" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="28" t="s">
         <v>27</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C117" s="29" t="s">
         <v>143</v>
@@ -8287,7 +8276,7 @@
         <v>93</v>
       </c>
       <c r="I117" s="30">
-        <v>20700</v>
+        <v>18000</v>
       </c>
       <c r="J117" s="29"/>
       <c r="K117" s="29" t="s">
@@ -8301,7 +8290,7 @@
         <v>27</v>
       </c>
       <c r="B118" s="40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C118" s="29" t="s">
         <v>143</v>
@@ -8320,7 +8309,7 @@
         <v>93</v>
       </c>
       <c r="I118" s="30">
-        <v>18000</v>
+        <v>5150</v>
       </c>
       <c r="J118" s="29"/>
       <c r="K118" s="29" t="s">
@@ -8333,27 +8322,27 @@
       <c r="A119" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B119" s="40" t="s">
-        <v>148</v>
+      <c r="B119" s="60" t="s">
+        <v>88</v>
       </c>
       <c r="C119" s="29" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="D119" s="29" t="s">
         <v>27</v>
       </c>
       <c r="E119" s="29" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="G119" s="29"/>
       <c r="H119" s="29" t="s">
         <v>93</v>
       </c>
       <c r="I119" s="30">
-        <v>5150</v>
+        <v>4025</v>
       </c>
       <c r="J119" s="29"/>
       <c r="K119" s="29" t="s">
@@ -8367,7 +8356,7 @@
         <v>27</v>
       </c>
       <c r="B120" s="60" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C120" s="29" t="s">
         <v>26</v>
@@ -8386,7 +8375,7 @@
         <v>93</v>
       </c>
       <c r="I120" s="30">
-        <v>4025</v>
+        <v>2300</v>
       </c>
       <c r="J120" s="29"/>
       <c r="K120" s="29" t="s">
@@ -8400,26 +8389,26 @@
         <v>27</v>
       </c>
       <c r="B121" s="60" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C121" s="29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D121" s="29" t="s">
         <v>27</v>
       </c>
       <c r="E121" s="29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F121" s="29" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="G121" s="29"/>
       <c r="H121" s="29" t="s">
         <v>93</v>
       </c>
       <c r="I121" s="30">
-        <v>2300</v>
+        <v>10000</v>
       </c>
       <c r="J121" s="29"/>
       <c r="K121" s="29" t="s">
@@ -8433,7 +8422,7 @@
         <v>27</v>
       </c>
       <c r="B122" s="60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C122" s="29" t="s">
         <v>28</v>
@@ -8466,7 +8455,7 @@
         <v>27</v>
       </c>
       <c r="B123" s="60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C123" s="29" t="s">
         <v>28</v>
@@ -8485,7 +8474,7 @@
         <v>93</v>
       </c>
       <c r="I123" s="30">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="J123" s="29"/>
       <c r="K123" s="29" t="s">
@@ -8499,7 +8488,7 @@
         <v>27</v>
       </c>
       <c r="B124" s="60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C124" s="29" t="s">
         <v>28</v>
@@ -8518,7 +8507,7 @@
         <v>93</v>
       </c>
       <c r="I124" s="30">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="J124" s="29"/>
       <c r="K124" s="29" t="s">
@@ -8532,7 +8521,7 @@
         <v>27</v>
       </c>
       <c r="B125" s="60" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C125" s="29" t="s">
         <v>28</v>
@@ -8565,7 +8554,7 @@
         <v>27</v>
       </c>
       <c r="B126" s="60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C126" s="29" t="s">
         <v>28</v>
@@ -8584,7 +8573,7 @@
         <v>93</v>
       </c>
       <c r="I126" s="30">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="J126" s="29"/>
       <c r="K126" s="29" t="s">
@@ -8594,37 +8583,19 @@
       <c r="M126" s="29"/>
     </row>
     <row r="127" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B127" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="C127" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D127" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E127" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F127" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G127" s="29"/>
-      <c r="H127" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="I127" s="30">
-        <v>10000</v>
-      </c>
-      <c r="J127" s="29"/>
-      <c r="K127" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="L127" s="29"/>
-      <c r="M127" s="29"/>
+      <c r="A127" s="56"/>
+      <c r="B127" s="59"/>
+      <c r="C127" s="57"/>
+      <c r="D127" s="57"/>
+      <c r="E127" s="57"/>
+      <c r="F127" s="57"/>
+      <c r="G127" s="57"/>
+      <c r="H127" s="57"/>
+      <c r="I127" s="55"/>
+      <c r="J127" s="57"/>
+      <c r="K127" s="57"/>
+      <c r="L127" s="57"/>
+      <c r="M127" s="57"/>
     </row>
     <row r="128" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="56"/>
@@ -8761,7 +8732,7 @@
       <c r="L136" s="57"/>
       <c r="M136" s="57"/>
     </row>
-    <row r="137" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="56"/>
       <c r="B137" s="59"/>
       <c r="C137" s="57"/>
@@ -8791,71 +8762,56 @@
       <c r="L138" s="57"/>
       <c r="M138" s="57"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A139" s="56"/>
-      <c r="B139" s="59"/>
-      <c r="C139" s="57"/>
-      <c r="D139" s="57"/>
-      <c r="E139" s="57"/>
-      <c r="F139" s="57"/>
-      <c r="G139" s="57"/>
-      <c r="H139" s="57"/>
-      <c r="I139" s="55"/>
-      <c r="J139" s="57"/>
-      <c r="K139" s="57"/>
-      <c r="L139" s="57"/>
-      <c r="M139" s="57"/>
-    </row>
-    <row r="141" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="140" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="141" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F141" s="80"/>
+      <c r="G141" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="H141" s="64">
+        <f>SUMIF(D2:D1023,"مدفوع",I2:I1023)-748000</f>
+        <v>605707.5399999998</v>
+      </c>
+    </row>
     <row r="142" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E142" s="67"/>
       <c r="F142" s="80"/>
-      <c r="G142" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="H142" s="64">
-        <f>SUMIF(D2:D1024,"مدفوع",I2:I1024)-748000</f>
-        <v>1605707.54</v>
+      <c r="G142" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H142" s="65">
+        <f>SUMIF(D2:D1023,"مستقبلي",I2:I1023)</f>
+        <v>130175</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E143" s="67"/>
       <c r="F143" s="80"/>
-      <c r="G143" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="H143" s="65">
-        <f>SUMIF(D2:D1024,"مستقبلي",I2:I1024)</f>
-        <v>130175</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G143" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="H143" s="66">
+        <f>SUMIF(D2:D1023,"مدفوع",I2:I1023)</f>
+        <v>1353707.5399999998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.3">
       <c r="E144" s="67"/>
-      <c r="F144" s="80"/>
-      <c r="G144" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="H144" s="66">
-        <f>SUMIF(D2:D1024,"مدفوع",I2:I1024)</f>
-        <v>2353707.54</v>
-      </c>
-    </row>
-    <row r="145" spans="5:8" ht="18" thickTop="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E145" s="67"/>
     </row>
-    <row r="146" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E146" s="67"/>
-    </row>
-    <row r="148" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E148" s="68"/>
-      <c r="H148" s="63"/>
+    <row r="147" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E147" s="68"/>
+      <c r="H147" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D139" xr:uid="{8DD4A2C2-2D88-4DA6-AAB9-88AA2C531F27}">
-      <formula1>$D$5:$D$139</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D138" xr:uid="{8DD4A2C2-2D88-4DA6-AAB9-88AA2C531F27}">
+      <formula1>$D$5:$D$138</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rehab_expenses.xlsx
+++ b/rehab_expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\New House\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8773E4F-E6C1-4588-AC83-A1B38C7990D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8923434E-AE33-4B24-AC44-F2BC0F6788B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="713" xr2:uid="{AB74FC30-BEBC-4B99-9425-710997B15428}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="289">
   <si>
     <t>مصروفات البيت</t>
   </si>
@@ -8175,19 +8175,45 @@
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="69"/>
-      <c r="B113" s="70"/>
-      <c r="C113" s="71"/>
-      <c r="D113" s="71"/>
-      <c r="E113" s="71"/>
-      <c r="F113" s="71"/>
-      <c r="G113" s="57"/>
-      <c r="H113" s="71"/>
-      <c r="I113" s="72"/>
-      <c r="J113" s="71"/>
-      <c r="K113" s="57"/>
-      <c r="L113" s="71"/>
-      <c r="M113" s="71"/>
+      <c r="A113" s="69">
+        <v>46188</v>
+      </c>
+      <c r="B113" s="70" t="s">
+        <v>288</v>
+      </c>
+      <c r="C113" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" s="71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="F113" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="G113" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="H113" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="I113" s="72">
+        <v>7000000</v>
+      </c>
+      <c r="J113" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="K113" s="71" t="s">
+        <v>237</v>
+      </c>
+      <c r="L113" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="M113" s="71" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="69"/>
@@ -8770,7 +8796,7 @@
       </c>
       <c r="H141" s="64">
         <f>SUMIF(D2:D1023,"مدفوع",I2:I1023)-748000</f>
-        <v>605707.5399999998</v>
+        <v>7605707.54</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -8792,7 +8818,7 @@
       </c>
       <c r="H143" s="66">
         <f>SUMIF(D2:D1023,"مدفوع",I2:I1023)</f>
-        <v>1353707.5399999998</v>
+        <v>8353707.54</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.3">

--- a/rehab_expenses.xlsx
+++ b/rehab_expenses.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\New House\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8923434E-AE33-4B24-AC44-F2BC0F6788B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF880DB-C621-4BC0-8211-DA41492BBA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="713" xr2:uid="{AB74FC30-BEBC-4B99-9425-710997B15428}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="289">
   <si>
     <t>مصروفات البيت</t>
   </si>
@@ -3364,8 +3364,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}" name="Table1" displayName="Table1" ref="A4:M138" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
-  <autoFilter ref="A4:M138" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}" name="Table1" displayName="Table1" ref="A4:M137" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+  <autoFilter ref="A4:M137" xr:uid="{02B48DBA-1A03-4B0D-8129-911F1B46E872}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{07A54FC1-E751-434C-8E2B-321DF3B580E1}" name="التاريخ" dataDxfId="63"/>
     <tableColumn id="2" xr3:uid="{402B6DF9-6739-4D62-9596-2B3A39BA29DE}" name="الوصف" dataDxfId="62"/>
@@ -3787,7 +3787,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B03AB583-00B0-4E1F-8550-C73216860618}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A2:M147"/>
+  <dimension ref="A2:M146"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" style="22" bestFit="1" customWidth="1"/>
@@ -8175,45 +8175,19 @@
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="69">
-        <v>46188</v>
-      </c>
-      <c r="B113" s="70" t="s">
-        <v>288</v>
-      </c>
-      <c r="C113" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="D113" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="F113" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="G113" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="H113" s="71" t="s">
-        <v>52</v>
-      </c>
-      <c r="I113" s="72">
-        <v>7000000</v>
-      </c>
-      <c r="J113" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="K113" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="L113" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="M113" s="71" t="s">
-        <v>10</v>
-      </c>
+      <c r="A113" s="69"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="71"/>
+      <c r="D113" s="71"/>
+      <c r="E113" s="71"/>
+      <c r="F113" s="71"/>
+      <c r="G113" s="57"/>
+      <c r="H113" s="71"/>
+      <c r="I113" s="72"/>
+      <c r="J113" s="71"/>
+      <c r="K113" s="57"/>
+      <c r="L113" s="71"/>
+      <c r="M113" s="71"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="69"/>
@@ -8222,35 +8196,53 @@
       <c r="D114" s="71"/>
       <c r="E114" s="71"/>
       <c r="F114" s="71"/>
-      <c r="G114" s="57"/>
+      <c r="G114" s="71"/>
       <c r="H114" s="71"/>
       <c r="I114" s="72"/>
       <c r="J114" s="71"/>
-      <c r="K114" s="57"/>
+      <c r="K114" s="71"/>
       <c r="L114" s="71"/>
       <c r="M114" s="71"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="69"/>
-      <c r="B115" s="70"/>
-      <c r="C115" s="71"/>
-      <c r="D115" s="71"/>
-      <c r="E115" s="71"/>
-      <c r="F115" s="71"/>
-      <c r="G115" s="71"/>
-      <c r="H115" s="71"/>
-      <c r="I115" s="72"/>
-      <c r="J115" s="71"/>
-      <c r="K115" s="71"/>
-      <c r="L115" s="71"/>
-      <c r="M115" s="71"/>
+    <row r="115" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B115" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C115" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="D115" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E115" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="F115" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="G115" s="29"/>
+      <c r="H115" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I115" s="30">
+        <v>20700</v>
+      </c>
+      <c r="J115" s="29"/>
+      <c r="K115" s="29" t="s">
+        <v>237</v>
+      </c>
+      <c r="L115" s="29"/>
+      <c r="M115" s="29"/>
     </row>
     <row r="116" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="28" t="s">
         <v>27</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C116" s="29" t="s">
         <v>143</v>
@@ -8269,7 +8261,7 @@
         <v>93</v>
       </c>
       <c r="I116" s="30">
-        <v>20700</v>
+        <v>18000</v>
       </c>
       <c r="J116" s="29"/>
       <c r="K116" s="29" t="s">
@@ -8283,7 +8275,7 @@
         <v>27</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C117" s="29" t="s">
         <v>143</v>
@@ -8302,7 +8294,7 @@
         <v>93</v>
       </c>
       <c r="I117" s="30">
-        <v>18000</v>
+        <v>5150</v>
       </c>
       <c r="J117" s="29"/>
       <c r="K117" s="29" t="s">
@@ -8315,27 +8307,27 @@
       <c r="A118" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B118" s="40" t="s">
-        <v>148</v>
+      <c r="B118" s="60" t="s">
+        <v>88</v>
       </c>
       <c r="C118" s="29" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="D118" s="29" t="s">
         <v>27</v>
       </c>
       <c r="E118" s="29" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="G118" s="29"/>
       <c r="H118" s="29" t="s">
         <v>93</v>
       </c>
       <c r="I118" s="30">
-        <v>5150</v>
+        <v>4025</v>
       </c>
       <c r="J118" s="29"/>
       <c r="K118" s="29" t="s">
@@ -8349,7 +8341,7 @@
         <v>27</v>
       </c>
       <c r="B119" s="60" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C119" s="29" t="s">
         <v>26</v>
@@ -8368,7 +8360,7 @@
         <v>93</v>
       </c>
       <c r="I119" s="30">
-        <v>4025</v>
+        <v>2300</v>
       </c>
       <c r="J119" s="29"/>
       <c r="K119" s="29" t="s">
@@ -8382,26 +8374,26 @@
         <v>27</v>
       </c>
       <c r="B120" s="60" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C120" s="29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D120" s="29" t="s">
         <v>27</v>
       </c>
       <c r="E120" s="29" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F120" s="29" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="G120" s="29"/>
       <c r="H120" s="29" t="s">
         <v>93</v>
       </c>
       <c r="I120" s="30">
-        <v>2300</v>
+        <v>10000</v>
       </c>
       <c r="J120" s="29"/>
       <c r="K120" s="29" t="s">
@@ -8415,7 +8407,7 @@
         <v>27</v>
       </c>
       <c r="B121" s="60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C121" s="29" t="s">
         <v>28</v>
@@ -8448,7 +8440,7 @@
         <v>27</v>
       </c>
       <c r="B122" s="60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C122" s="29" t="s">
         <v>28</v>
@@ -8467,7 +8459,7 @@
         <v>93</v>
       </c>
       <c r="I122" s="30">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="J122" s="29"/>
       <c r="K122" s="29" t="s">
@@ -8481,7 +8473,7 @@
         <v>27</v>
       </c>
       <c r="B123" s="60" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C123" s="29" t="s">
         <v>28</v>
@@ -8500,7 +8492,7 @@
         <v>93</v>
       </c>
       <c r="I123" s="30">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="J123" s="29"/>
       <c r="K123" s="29" t="s">
@@ -8514,7 +8506,7 @@
         <v>27</v>
       </c>
       <c r="B124" s="60" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C124" s="29" t="s">
         <v>28</v>
@@ -8547,7 +8539,7 @@
         <v>27</v>
       </c>
       <c r="B125" s="60" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C125" s="29" t="s">
         <v>28</v>
@@ -8566,7 +8558,7 @@
         <v>93</v>
       </c>
       <c r="I125" s="30">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="J125" s="29"/>
       <c r="K125" s="29" t="s">
@@ -8576,37 +8568,19 @@
       <c r="M125" s="29"/>
     </row>
     <row r="126" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="B126" s="60" t="s">
-        <v>108</v>
-      </c>
-      <c r="C126" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D126" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E126" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="F126" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G126" s="29"/>
-      <c r="H126" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="I126" s="30">
-        <v>10000</v>
-      </c>
-      <c r="J126" s="29"/>
-      <c r="K126" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="L126" s="29"/>
-      <c r="M126" s="29"/>
+      <c r="A126" s="56"/>
+      <c r="B126" s="59"/>
+      <c r="C126" s="57"/>
+      <c r="D126" s="57"/>
+      <c r="E126" s="57"/>
+      <c r="F126" s="57"/>
+      <c r="G126" s="57"/>
+      <c r="H126" s="57"/>
+      <c r="I126" s="55"/>
+      <c r="J126" s="57"/>
+      <c r="K126" s="57"/>
+      <c r="L126" s="57"/>
+      <c r="M126" s="57"/>
     </row>
     <row r="127" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="56"/>
@@ -8743,7 +8717,7 @@
       <c r="L135" s="57"/>
       <c r="M135" s="57"/>
     </row>
-    <row r="136" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="56"/>
       <c r="B136" s="59"/>
       <c r="C136" s="57"/>
@@ -8773,71 +8747,56 @@
       <c r="L137" s="57"/>
       <c r="M137" s="57"/>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A138" s="56"/>
-      <c r="B138" s="59"/>
-      <c r="C138" s="57"/>
-      <c r="D138" s="57"/>
-      <c r="E138" s="57"/>
-      <c r="F138" s="57"/>
-      <c r="G138" s="57"/>
-      <c r="H138" s="57"/>
-      <c r="I138" s="55"/>
-      <c r="J138" s="57"/>
-      <c r="K138" s="57"/>
-      <c r="L138" s="57"/>
-      <c r="M138" s="57"/>
-    </row>
-    <row r="140" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="139" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="140" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F140" s="80"/>
+      <c r="G140" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="H140" s="64">
+        <f>SUMIF(D2:D1022,"مدفوع",I2:I1022)-748000</f>
+        <v>605707.5399999998</v>
+      </c>
+    </row>
     <row r="141" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E141" s="67"/>
       <c r="F141" s="80"/>
-      <c r="G141" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="H141" s="64">
-        <f>SUMIF(D2:D1023,"مدفوع",I2:I1023)-748000</f>
-        <v>7605707.54</v>
+      <c r="G141" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H141" s="65">
+        <f>SUMIF(D2:D1022,"مستقبلي",I2:I1022)</f>
+        <v>130175</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E142" s="67"/>
       <c r="F142" s="80"/>
-      <c r="G142" s="38" t="s">
-        <v>229</v>
-      </c>
-      <c r="H142" s="65">
-        <f>SUMIF(D2:D1023,"مستقبلي",I2:I1023)</f>
-        <v>130175</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G142" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="H142" s="66">
+        <f>SUMIF(D2:D1022,"مدفوع",I2:I1022)</f>
+        <v>1353707.5399999998</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.3">
       <c r="E143" s="67"/>
-      <c r="F143" s="80"/>
-      <c r="G143" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="H143" s="66">
-        <f>SUMIF(D2:D1023,"مدفوع",I2:I1023)</f>
-        <v>8353707.54</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="18" thickTop="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E144" s="67"/>
     </row>
-    <row r="145" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E145" s="67"/>
-    </row>
-    <row r="147" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E147" s="68"/>
-      <c r="H147" s="63"/>
+    <row r="146" spans="5:8" x14ac:dyDescent="0.3">
+      <c r="E146" s="68"/>
+      <c r="H146" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D138" xr:uid="{8DD4A2C2-2D88-4DA6-AAB9-88AA2C531F27}">
-      <formula1>$D$5:$D$138</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D137" xr:uid="{8DD4A2C2-2D88-4DA6-AAB9-88AA2C531F27}">
+      <formula1>$D$5:$D$137</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/rehab_expenses.xlsx
+++ b/rehab_expenses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\New House\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E45D53DF-6B75-D947-9C0D-D1094C2CD388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CE3E4E-26D3-4B56-9F98-DA9EF830095B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="713" xr2:uid="{AB74FC30-BEBC-4B99-9425-710997B15428}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="294">
   <si>
     <t>مصروفات البيت</t>
   </si>
@@ -1045,21 +1045,6 @@
     <t>ماء بارد لصبية أعمدة الدور الأول</t>
   </si>
   <si>
-    <t>1111 متر مكعب ضغط 4000</t>
-  </si>
-  <si>
-    <t>ارجو تحديث عدد ال م 3 لصبية يوم الخميس</t>
-  </si>
-  <si>
-    <t>ارجو تحديث عدد ال م 3 للماء البارد لصبية يوم الخميس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صبية أعمدة الدور الأول
-96 م3
-4000 psi
-289.75 ريال للمتر المكعب </t>
-  </si>
-  <si>
     <t>ماء بارد لصبية أعمدة الدور الأول
 96 م3
  5.75 ريال لكل متر مكعب</t>
@@ -1075,6 +1060,15 @@
   </si>
   <si>
     <t xml:space="preserve"> كاش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صبية أعمدة الدور الأول
+15 م3
+4000 psi
+289.75 ريال للمتر المكعب </t>
+  </si>
+  <si>
+    <t>15 متر مكعب ضغط 4000</t>
   </si>
 </sst>
 </file>
@@ -1082,9 +1076,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="[$SAR]\ #,##0.00"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="[$SAR]\ #,##0.00"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1158,7 +1152,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1192,12 +1186,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1339,17 +1327,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1360,11 +1348,11 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="distributed"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1373,11 +1361,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1390,35 +1378,35 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1433,15 +1421,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1452,11 +1440,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1471,25 +1459,25 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1498,7 +1486,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1510,40 +1498,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="39" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="distributed"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1554,6 +1530,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1736,7 +1724,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1991,7 +1979,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2128,7 +2116,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="[$SAR]\ #,##0.00"/>
+      <numFmt numFmtId="165" formatCode="[$SAR]\ #,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
@@ -2277,7 +2265,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2526,7 +2514,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2681,7 +2669,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="167" formatCode="#,##0.00_);\(#,##0.00\)"/>
+      <numFmt numFmtId="7" formatCode="#,##0.00_);\(#,##0.00\)"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
@@ -2868,7 +2856,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -3091,7 +3079,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="[$SAR]\ #,##0.00"/>
+      <numFmt numFmtId="165" formatCode="[$SAR]\ #,##0.00"/>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -3336,7 +3324,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3821,43 +3809,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B03AB583-00B0-4E1F-8550-C73216860618}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A2:M149"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.48046875" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="134.38671875" style="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.68359375" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.68359375" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="19.37109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="42.375" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.1484375" style="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.8671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="134.33203125" style="58" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="19.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="42.33203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.88671875" style="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.33203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.97265625" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.91796875" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.66015625" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.7421875" style="21"/>
-    <col min="15" max="15" width="6.859375" style="21" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.7421875" style="21"/>
+    <col min="11" max="11" width="12" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="21"/>
+    <col min="15" max="15" width="6.88671875" style="21" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.77734375" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+    <row r="2" spans="1:13" ht="37.799999999999997" x14ac:dyDescent="0.3">
+      <c r="A2" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-    </row>
-    <row r="4" spans="1:13" s="25" customFormat="1" ht="33" x14ac:dyDescent="0.2">
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+    </row>
+    <row r="4" spans="1:13" s="25" customFormat="1" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
@@ -3898,7 +3886,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="69">
         <v>45302</v>
       </c>
@@ -3936,7 +3924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="69">
         <v>45448</v>
       </c>
@@ -3975,7 +3963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="69">
         <v>45475</v>
       </c>
@@ -4016,7 +4004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="69">
         <v>45538</v>
       </c>
@@ -4055,7 +4043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="69">
         <v>45543</v>
       </c>
@@ -4096,7 +4084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A10" s="69">
         <v>45683</v>
       </c>
@@ -4137,7 +4125,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A11" s="69">
         <v>45684</v>
       </c>
@@ -4178,7 +4166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="69">
         <v>45768</v>
       </c>
@@ -4219,7 +4207,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="69">
         <v>45943</v>
       </c>
@@ -4260,7 +4248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="69">
         <v>46012</v>
       </c>
@@ -4299,7 +4287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="69">
         <v>46014</v>
       </c>
@@ -4340,7 +4328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="162" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="174" x14ac:dyDescent="0.3">
       <c r="A16" s="69">
         <v>46014</v>
       </c>
@@ -4379,7 +4367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="69">
         <v>46014</v>
       </c>
@@ -4418,7 +4406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="69">
         <v>46019</v>
       </c>
@@ -4459,7 +4447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="69">
         <v>46019</v>
       </c>
@@ -4500,7 +4488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="69">
         <v>46019</v>
       </c>
@@ -4539,7 +4527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="69">
         <v>46019</v>
       </c>
@@ -4580,7 +4568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="69">
         <v>46022</v>
       </c>
@@ -4621,7 +4609,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="69">
         <v>46022</v>
       </c>
@@ -4662,7 +4650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="69">
         <v>46023</v>
       </c>
@@ -4701,7 +4689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="69">
         <v>46023</v>
       </c>
@@ -4742,7 +4730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="69">
         <v>46025</v>
       </c>
@@ -4783,7 +4771,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="69">
         <v>46026</v>
       </c>
@@ -4824,7 +4812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="69">
         <v>46026</v>
       </c>
@@ -4865,7 +4853,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="69">
         <v>46027</v>
       </c>
@@ -4904,7 +4892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="69">
         <v>46027</v>
       </c>
@@ -4945,7 +4933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A31" s="69">
         <v>46028</v>
       </c>
@@ -4984,7 +4972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A32" s="69">
         <v>46028</v>
       </c>
@@ -5025,7 +5013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="69">
         <v>46029</v>
       </c>
@@ -5064,7 +5052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="69">
         <v>46030</v>
       </c>
@@ -5105,7 +5093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="69">
         <v>46031</v>
       </c>
@@ -5144,7 +5132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="69">
         <v>46032</v>
       </c>
@@ -5181,7 +5169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A37" s="69">
         <v>46037</v>
       </c>
@@ -5220,7 +5208,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24">
         <v>46041</v>
       </c>
@@ -5259,7 +5247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="75" customFormat="1" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" s="75" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A39" s="69">
         <v>46042</v>
       </c>
@@ -5300,7 +5288,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="113.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" ht="121.8" x14ac:dyDescent="0.3">
       <c r="A40" s="69">
         <v>46046</v>
       </c>
@@ -5339,7 +5327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="97.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" ht="104.4" x14ac:dyDescent="0.3">
       <c r="A41" s="69">
         <v>46046</v>
       </c>
@@ -5378,7 +5366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="69">
         <v>46047</v>
       </c>
@@ -5417,7 +5405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A43" s="69">
         <v>46048</v>
       </c>
@@ -5456,7 +5444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="69">
         <v>46051</v>
       </c>
@@ -5495,7 +5483,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="69">
         <v>46051</v>
       </c>
@@ -5534,7 +5522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="81" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" ht="87" x14ac:dyDescent="0.3">
       <c r="A46" s="69">
         <v>46052</v>
       </c>
@@ -5573,7 +5561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A47" s="69">
         <v>46054</v>
       </c>
@@ -5612,7 +5600,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A48" s="69">
         <v>46054</v>
       </c>
@@ -5653,7 +5641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="69">
         <v>46055</v>
       </c>
@@ -5692,7 +5680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A50" s="69">
         <v>46056</v>
       </c>
@@ -5733,7 +5721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="69">
         <v>46060</v>
       </c>
@@ -5772,7 +5760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="69">
         <v>46060</v>
       </c>
@@ -5811,7 +5799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="69">
         <v>46063</v>
       </c>
@@ -5852,7 +5840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="69">
         <v>46063</v>
       </c>
@@ -5891,7 +5879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A55" s="69">
         <v>46064</v>
       </c>
@@ -5930,7 +5918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A56" s="69">
         <v>46064</v>
       </c>
@@ -5969,7 +5957,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="69">
         <v>46064</v>
       </c>
@@ -6010,7 +5998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A58" s="69">
         <v>46065</v>
       </c>
@@ -6051,7 +6039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="69">
         <v>46076</v>
       </c>
@@ -6090,7 +6078,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A60" s="69">
         <v>46077</v>
       </c>
@@ -6131,7 +6119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="69">
         <v>46077</v>
       </c>
@@ -6170,7 +6158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="69">
         <v>46077</v>
       </c>
@@ -6209,7 +6197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="69">
         <v>46078</v>
       </c>
@@ -6248,7 +6236,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="69">
         <v>46081</v>
       </c>
@@ -6289,7 +6277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="69">
         <v>46083</v>
       </c>
@@ -6328,7 +6316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="69">
         <v>46083</v>
       </c>
@@ -6369,7 +6357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="69">
         <v>46085</v>
       </c>
@@ -6408,7 +6396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A68" s="69">
         <v>46092</v>
       </c>
@@ -6447,7 +6435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="69">
         <v>46092</v>
       </c>
@@ -6488,7 +6476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="69">
         <v>46092</v>
       </c>
@@ -6529,7 +6517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="69">
         <v>46093</v>
       </c>
@@ -6570,7 +6558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="69">
         <v>46098</v>
       </c>
@@ -6611,7 +6599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A73" s="69">
         <v>46099</v>
       </c>
@@ -6652,7 +6640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="69">
         <v>46105</v>
       </c>
@@ -6691,7 +6679,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A75" s="69">
         <v>46109</v>
       </c>
@@ -6730,7 +6718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="69">
         <v>46114</v>
       </c>
@@ -6771,7 +6759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="69">
         <v>46117</v>
       </c>
@@ -6810,7 +6798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="81" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" ht="87" x14ac:dyDescent="0.3">
       <c r="A78" s="69">
         <v>46117</v>
       </c>
@@ -6849,7 +6837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A79" s="69">
         <v>46118</v>
       </c>
@@ -6890,7 +6878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" s="75" customFormat="1" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" s="75" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A80" s="69">
         <v>46120</v>
       </c>
@@ -6931,7 +6919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A81" s="69">
         <v>46120</v>
       </c>
@@ -6970,7 +6958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" s="75" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="69">
         <v>46123</v>
       </c>
@@ -7011,7 +6999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="69">
         <v>46123</v>
       </c>
@@ -7050,7 +7038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="69">
         <v>46125</v>
       </c>
@@ -7089,7 +7077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="69">
         <v>46126</v>
       </c>
@@ -7130,7 +7118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A86" s="69">
         <v>46127</v>
       </c>
@@ -7169,7 +7157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="33" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" ht="34.799999999999997" x14ac:dyDescent="0.3">
       <c r="A87" s="69">
         <v>46131</v>
       </c>
@@ -7210,7 +7198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="69">
         <v>46131</v>
       </c>
@@ -7251,7 +7239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A89" s="69">
         <v>46132</v>
       </c>
@@ -7290,7 +7278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="216" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="69">
         <v>46121</v>
       </c>
@@ -7331,7 +7319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="215.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" ht="215.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="69">
         <v>46137</v>
       </c>
@@ -7372,7 +7360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="69">
         <v>46139</v>
       </c>
@@ -7413,7 +7401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="69">
         <v>46140</v>
       </c>
@@ -7454,7 +7442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A94" s="69">
         <v>46145</v>
       </c>
@@ -7493,7 +7481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:13" s="75" customFormat="1" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" s="75" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A95" s="69">
         <v>46145</v>
       </c>
@@ -7534,7 +7522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:13" s="75" customFormat="1" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" s="75" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A96" s="69">
         <v>46152</v>
       </c>
@@ -7575,7 +7563,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="97" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="56">
         <v>46153</v>
       </c>
@@ -7608,7 +7596,7 @@
       <c r="L97" s="57"/>
       <c r="M97" s="57"/>
     </row>
-    <row r="98" spans="1:13" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A98" s="69">
         <v>46155</v>
       </c>
@@ -7647,7 +7635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="69">
         <v>46155</v>
       </c>
@@ -7688,7 +7676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="69">
         <v>46155</v>
       </c>
@@ -7729,7 +7717,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="129.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" ht="139.19999999999999" x14ac:dyDescent="0.3">
       <c r="A101" s="69">
         <v>46161</v>
       </c>
@@ -7768,7 +7756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="69">
         <v>46173</v>
       </c>
@@ -7809,7 +7797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A103" s="69">
         <v>46173</v>
       </c>
@@ -7850,7 +7838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="69">
         <v>46179</v>
       </c>
@@ -7891,7 +7879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="69">
         <v>46180</v>
       </c>
@@ -7930,7 +7918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:13" s="75" customFormat="1" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" s="75" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A106" s="69">
         <v>46181</v>
       </c>
@@ -7971,7 +7959,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:13" s="75" customFormat="1" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" s="75" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A107" s="69">
         <v>46181</v>
       </c>
@@ -8012,7 +8000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A108" s="69">
         <v>46181</v>
       </c>
@@ -8051,7 +8039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="69">
         <v>46182</v>
       </c>
@@ -8088,7 +8076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="69">
         <v>46182</v>
       </c>
@@ -8125,7 +8113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="69">
         <v>46183</v>
       </c>
@@ -8166,7 +8154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="69">
         <v>46188</v>
       </c>
@@ -8207,12 +8195,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:13" s="75" customFormat="1" ht="65.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" s="75" customFormat="1" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A113" s="69">
         <v>46190</v>
       </c>
-      <c r="B113" s="87" t="s">
-        <v>290</v>
+      <c r="B113" s="90" t="s">
+        <v>292</v>
       </c>
       <c r="C113" s="73" t="s">
         <v>127</v>
@@ -8227,13 +8215,13 @@
         <v>239</v>
       </c>
       <c r="G113" s="71" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H113" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="I113" s="88">
-        <v>4056.5</v>
+      <c r="I113" s="89">
+        <v>4346.25</v>
       </c>
       <c r="J113" s="71" t="s">
         <v>54</v>
@@ -8248,12 +8236,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:13" s="75" customFormat="1" ht="48.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" s="75" customFormat="1" ht="52.2" x14ac:dyDescent="0.3">
       <c r="A114" s="69">
         <v>46190</v>
       </c>
-      <c r="B114" s="87" t="s">
-        <v>291</v>
+      <c r="B114" s="90" t="s">
+        <v>287</v>
       </c>
       <c r="C114" s="73" t="s">
         <v>127</v>
@@ -8268,13 +8256,13 @@
         <v>239</v>
       </c>
       <c r="G114" s="71" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H114" s="71" t="s">
         <v>93</v>
       </c>
-      <c r="I114" s="88">
-        <v>552</v>
+      <c r="I114" s="89">
+        <v>86.25</v>
       </c>
       <c r="J114" s="71" t="s">
         <v>54</v>
@@ -8289,7 +8277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="56">
         <v>46191</v>
       </c>
@@ -8316,7 +8304,7 @@
         <v>10000</v>
       </c>
       <c r="J115" s="57" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="K115" s="57" t="s">
         <v>237</v>
@@ -8326,7 +8314,7 @@
       </c>
       <c r="M115" s="57"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="69"/>
       <c r="B116" s="70"/>
       <c r="C116" s="71"/>
@@ -8341,7 +8329,7 @@
       <c r="L116" s="71"/>
       <c r="M116" s="71"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="69"/>
       <c r="B117" s="70"/>
       <c r="C117" s="71"/>
@@ -8356,7 +8344,7 @@
       <c r="L117" s="71"/>
       <c r="M117" s="71"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="69"/>
       <c r="B118" s="70"/>
       <c r="C118" s="71"/>
@@ -8371,7 +8359,7 @@
       <c r="L118" s="71"/>
       <c r="M118" s="71"/>
     </row>
-    <row r="119" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="28" t="s">
         <v>27</v>
       </c>
@@ -8404,7 +8392,7 @@
       <c r="L119" s="29"/>
       <c r="M119" s="29"/>
     </row>
-    <row r="120" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="28" t="s">
         <v>27</v>
       </c>
@@ -8437,7 +8425,7 @@
       <c r="L120" s="29"/>
       <c r="M120" s="29"/>
     </row>
-    <row r="121" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="28" t="s">
         <v>27</v>
       </c>
@@ -8470,7 +8458,7 @@
       <c r="L121" s="29"/>
       <c r="M121" s="29"/>
     </row>
-    <row r="122" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="28" t="s">
         <v>27</v>
       </c>
@@ -8503,7 +8491,7 @@
       <c r="L122" s="29"/>
       <c r="M122" s="29"/>
     </row>
-    <row r="123" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="28" t="s">
         <v>27</v>
       </c>
@@ -8536,7 +8524,7 @@
       <c r="L123" s="29"/>
       <c r="M123" s="29"/>
     </row>
-    <row r="124" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="28" t="s">
         <v>27</v>
       </c>
@@ -8569,7 +8557,7 @@
       <c r="L124" s="29"/>
       <c r="M124" s="29"/>
     </row>
-    <row r="125" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="28" t="s">
         <v>27</v>
       </c>
@@ -8602,7 +8590,7 @@
       <c r="L125" s="29"/>
       <c r="M125" s="29"/>
     </row>
-    <row r="126" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="28" t="s">
         <v>27</v>
       </c>
@@ -8635,7 +8623,7 @@
       <c r="L126" s="29"/>
       <c r="M126" s="29"/>
     </row>
-    <row r="127" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="28" t="s">
         <v>27</v>
       </c>
@@ -8668,7 +8656,7 @@
       <c r="L127" s="29"/>
       <c r="M127" s="29"/>
     </row>
-    <row r="128" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="28" t="s">
         <v>27</v>
       </c>
@@ -8701,7 +8689,7 @@
       <c r="L128" s="29"/>
       <c r="M128" s="29"/>
     </row>
-    <row r="129" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="56"/>
       <c r="B129" s="59"/>
       <c r="C129" s="57"/>
@@ -8716,7 +8704,7 @@
       <c r="L129" s="57"/>
       <c r="M129" s="57"/>
     </row>
-    <row r="130" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="56"/>
       <c r="B130" s="59"/>
       <c r="C130" s="57"/>
@@ -8731,7 +8719,7 @@
       <c r="L130" s="57"/>
       <c r="M130" s="57"/>
     </row>
-    <row r="131" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="56"/>
       <c r="B131" s="59"/>
       <c r="C131" s="57"/>
@@ -8746,7 +8734,7 @@
       <c r="L131" s="57"/>
       <c r="M131" s="57"/>
     </row>
-    <row r="132" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="56"/>
       <c r="B132" s="59"/>
       <c r="C132" s="57"/>
@@ -8761,7 +8749,7 @@
       <c r="L132" s="57"/>
       <c r="M132" s="57"/>
     </row>
-    <row r="133" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="56"/>
       <c r="B133" s="59"/>
       <c r="C133" s="57"/>
@@ -8776,7 +8764,7 @@
       <c r="L133" s="57"/>
       <c r="M133" s="57"/>
     </row>
-    <row r="134" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="56"/>
       <c r="B134" s="59"/>
       <c r="C134" s="57"/>
@@ -8791,7 +8779,7 @@
       <c r="L134" s="57"/>
       <c r="M134" s="57"/>
     </row>
-    <row r="135" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="56"/>
       <c r="B135" s="59"/>
       <c r="C135" s="57"/>
@@ -8806,7 +8794,7 @@
       <c r="L135" s="57"/>
       <c r="M135" s="57"/>
     </row>
-    <row r="136" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="56"/>
       <c r="B136" s="59"/>
       <c r="C136" s="57"/>
@@ -8821,7 +8809,7 @@
       <c r="L136" s="57"/>
       <c r="M136" s="57"/>
     </row>
-    <row r="137" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="56"/>
       <c r="B137" s="59"/>
       <c r="C137" s="57"/>
@@ -8836,7 +8824,7 @@
       <c r="L137" s="57"/>
       <c r="M137" s="57"/>
     </row>
-    <row r="138" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="56"/>
       <c r="B138" s="59"/>
       <c r="C138" s="57"/>
@@ -8851,7 +8839,7 @@
       <c r="L138" s="57"/>
       <c r="M138" s="57"/>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="56"/>
       <c r="B139" s="59"/>
       <c r="C139" s="57"/>
@@ -8866,7 +8854,7 @@
       <c r="L139" s="57"/>
       <c r="M139" s="57"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="56"/>
       <c r="B140" s="59"/>
       <c r="C140" s="57"/>
@@ -8881,18 +8869,18 @@
       <c r="L140" s="57"/>
       <c r="M140" s="57"/>
     </row>
-    <row r="142" spans="1:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:13" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="143" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F143" s="80"/>
       <c r="G143" s="37" t="s">
         <v>230</v>
       </c>
       <c r="H143" s="64">
         <f>SUMIF(D2:D1025,"مدفوع",I2:I1025)-748000</f>
-        <v>620316.0399999998</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>620140.0399999998</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E144" s="67"/>
       <c r="F144" s="80"/>
       <c r="G144" s="38" t="s">
@@ -8903,7 +8891,7 @@
         <v>120175</v>
       </c>
     </row>
-    <row r="145" spans="5:8" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="5:8" ht="25.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E145" s="67"/>
       <c r="F145" s="80"/>
       <c r="G145" s="39" t="s">
@@ -8911,16 +8899,16 @@
       </c>
       <c r="H145" s="66">
         <f>SUMIF(D2:D1025,"مدفوع",I2:I1025)</f>
-        <v>1368316.0399999998</v>
-      </c>
-    </row>
-    <row r="146" spans="5:8" ht="18.75" thickTop="1" x14ac:dyDescent="0.2">
+        <v>1368140.0399999998</v>
+      </c>
+    </row>
+    <row r="146" spans="5:8" ht="18" thickTop="1" x14ac:dyDescent="0.3">
       <c r="E146" s="67"/>
     </row>
-    <row r="147" spans="5:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E147" s="67"/>
     </row>
-    <row r="149" spans="5:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E149" s="68"/>
       <c r="H149" s="63"/>
     </row>
@@ -8945,24 +8933,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8BE8CA6-53FA-4C7F-8D77-23C70A60C36D}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A3:L53"/>
-  <sheetFormatPr defaultColWidth="22.8671875" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.92578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.96484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.46875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.390625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.71875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="51.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.1875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="22.8671875" style="2"/>
+    <col min="1" max="1" width="21.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="51.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="22.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="37.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" ht="39" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>149</v>
       </c>
@@ -8974,7 +8962,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="5" spans="1:11" s="7" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" s="7" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
@@ -9003,7 +8991,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="43">
         <v>46042</v>
       </c>
@@ -9034,7 +9022,7 @@
       </c>
       <c r="K6" s="52"/>
     </row>
-    <row r="7" spans="1:11" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A7" s="47">
         <v>46042</v>
       </c>
@@ -9065,7 +9053,7 @@
       </c>
       <c r="K7" s="53"/>
     </row>
-    <row r="8" spans="1:11" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A8" s="47">
         <v>46054</v>
       </c>
@@ -9092,7 +9080,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9" s="43">
         <v>46055</v>
       </c>
@@ -9123,7 +9111,7 @@
       </c>
       <c r="K9" s="52"/>
     </row>
-    <row r="10" spans="1:11" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A10" s="47">
         <v>46055</v>
       </c>
@@ -9150,7 +9138,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11" s="43">
         <v>46064</v>
       </c>
@@ -9177,7 +9165,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A12" s="47">
         <v>46064</v>
       </c>
@@ -9204,7 +9192,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13" s="43">
         <v>46075</v>
       </c>
@@ -9231,7 +9219,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14" s="43">
         <v>46077</v>
       </c>
@@ -9258,7 +9246,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A15" s="47">
         <v>46077</v>
       </c>
@@ -9285,7 +9273,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16" s="43">
         <v>46096</v>
       </c>
@@ -9312,7 +9300,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A17" s="47">
         <v>46099</v>
       </c>
@@ -9339,7 +9327,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="43">
         <v>46116</v>
       </c>
@@ -9366,7 +9354,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A19" s="47">
         <v>46120</v>
       </c>
@@ -9393,7 +9381,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="43">
         <v>46144</v>
       </c>
@@ -9420,7 +9408,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A21" s="47">
         <v>46145</v>
       </c>
@@ -9447,7 +9435,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="43">
         <v>46151</v>
       </c>
@@ -9474,7 +9462,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A23" s="47">
         <v>46152</v>
       </c>
@@ -9501,7 +9489,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="43">
         <v>46180</v>
       </c>
@@ -9528,7 +9516,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="43">
         <v>46180</v>
       </c>
@@ -9555,7 +9543,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A26" s="47">
         <v>46181</v>
       </c>
@@ -9582,7 +9570,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="59.4" x14ac:dyDescent="0.4">
       <c r="A27" s="47">
         <v>46181</v>
       </c>
@@ -9609,7 +9597,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="43">
         <v>46180</v>
       </c>
@@ -9635,7 +9623,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="43">
         <v>46190</v>
       </c>
@@ -9662,15 +9650,15 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="55.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A30" s="47">
         <v>46181</v>
       </c>
       <c r="B30" s="48" t="s">
         <v>285</v>
       </c>
-      <c r="C30" s="81" t="s">
-        <v>287</v>
+      <c r="C30" s="94" t="s">
+        <v>293</v>
       </c>
       <c r="D30" s="52" t="s">
         <v>165</v>
@@ -9678,29 +9666,27 @@
       <c r="E30" s="49">
         <v>289.75</v>
       </c>
-      <c r="F30" s="82">
-        <v>-14</v>
+      <c r="F30" s="93">
+        <v>-15</v>
       </c>
       <c r="G30" s="50">
         <f>Table83[[#This Row],[سعر المتر]]*Table83[[#This Row],[الكمية]]</f>
-        <v>-4056.5</v>
+        <v>-4346.25</v>
       </c>
       <c r="H30" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="I30" s="83" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="55.5" x14ac:dyDescent="0.3">
+      <c r="I30" s="92"/>
+    </row>
+    <row r="31" spans="1:9" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A31" s="47">
         <v>46181</v>
       </c>
       <c r="B31" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="C31" s="81" t="s">
-        <v>287</v>
+      <c r="C31" s="94" t="s">
+        <v>293</v>
       </c>
       <c r="D31" s="52" t="s">
         <v>165</v>
@@ -9708,24 +9694,22 @@
       <c r="E31" s="49">
         <v>5.75</v>
       </c>
-      <c r="F31" s="82">
-        <v>-14</v>
+      <c r="F31" s="93">
+        <v>-15</v>
       </c>
       <c r="G31" s="50">
         <f>Table83[[#This Row],[سعر المتر]]*Table83[[#This Row],[الكمية]]</f>
-        <v>-80.5</v>
+        <v>-86.25</v>
       </c>
       <c r="H31" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="I31" s="83" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I31" s="92"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="44"/>
-      <c r="C32" s="86"/>
+      <c r="C32" s="83"/>
       <c r="D32" s="8"/>
       <c r="E32" s="33"/>
       <c r="F32" s="8"/>
@@ -9735,10 +9719,10 @@
       </c>
       <c r="H32" s="16"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" s="15"/>
       <c r="B33" s="44"/>
-      <c r="C33" s="86"/>
+      <c r="C33" s="83"/>
       <c r="D33" s="8"/>
       <c r="E33" s="33"/>
       <c r="F33" s="8"/>
@@ -9748,33 +9732,33 @@
       </c>
       <c r="H33" s="16"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34" s="15"/>
       <c r="B34" s="44"/>
       <c r="C34" s="32"/>
       <c r="D34" s="1"/>
       <c r="E34" s="32"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="85">
+      <c r="G34" s="82">
         <f>Table83[[#This Row],[سعر المتر]]*Table83[[#This Row],[الكمية]]</f>
         <v>0</v>
       </c>
       <c r="H34" s="16"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35" s="15"/>
       <c r="B35" s="14"/>
-      <c r="C35" s="84"/>
+      <c r="C35" s="81"/>
       <c r="D35" s="1"/>
       <c r="E35" s="32"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="85">
+      <c r="G35" s="82">
         <f>Table83[[#This Row],[سعر المتر]]*Table83[[#This Row],[الكمية]]</f>
         <v>0</v>
       </c>
       <c r="H35" s="16"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36" s="31"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -9787,68 +9771,42 @@
       </c>
       <c r="H36" s="35"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J37" s="91"/>
-      <c r="K37" s="91"/>
-      <c r="L37" s="91"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J37" s="85"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="F38" s="9" t="s">
         <v>150</v>
       </c>
       <c r="G38" s="41">
         <f>SUM(G6:G36)</f>
-        <v>1078.5</v>
-      </c>
-      <c r="J38" s="89"/>
-      <c r="K38" s="89"/>
-      <c r="L38" s="89"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J39" s="89"/>
-      <c r="K39" s="89"/>
-      <c r="L39" s="89"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="F40" s="9" t="s">
         <v>201</v>
       </c>
       <c r="G40" s="41">
         <f>G38/J48</f>
-        <v>3.7221742881794651</v>
-      </c>
-      <c r="J40" s="89"/>
-      <c r="K40" s="89"/>
-      <c r="L40" s="89"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="89"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J42" s="91"/>
-      <c r="K42" s="91"/>
-      <c r="L42" s="91"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J43" s="89"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="89"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J44" s="89"/>
-      <c r="K44" s="89"/>
-      <c r="L44" s="89"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J46" s="92" t="s">
-        <v>293</v>
-      </c>
-      <c r="K46" s="92"/>
-      <c r="L46" s="92"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+        <v>2.7023295944779981</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J42" s="85"/>
+      <c r="K42" s="85"/>
+      <c r="L42" s="85"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J46" s="86" t="s">
+        <v>289</v>
+      </c>
+      <c r="K46" s="86"/>
+      <c r="L46" s="86"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J47" s="1" t="s">
         <v>166</v>
       </c>
@@ -9859,26 +9817,26 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J48" s="1">
         <v>289.75</v>
       </c>
       <c r="K48" s="1">
-        <v>14</v>
-      </c>
-      <c r="L48" s="1">
+        <v>15</v>
+      </c>
+      <c r="L48" s="91">
         <f>J48*K48</f>
-        <v>4056.5</v>
-      </c>
-    </row>
-    <row r="51" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J51" s="93" t="s">
-        <v>294</v>
-      </c>
-      <c r="K51" s="93"/>
-      <c r="L51" s="93"/>
-    </row>
-    <row r="52" spans="10:12" x14ac:dyDescent="0.3">
+        <v>4346.25</v>
+      </c>
+    </row>
+    <row r="51" spans="10:12" x14ac:dyDescent="0.4">
+      <c r="J51" s="87" t="s">
+        <v>290</v>
+      </c>
+      <c r="K51" s="87"/>
+      <c r="L51" s="87"/>
+    </row>
+    <row r="52" spans="10:12" x14ac:dyDescent="0.4">
       <c r="J52" s="1" t="s">
         <v>166</v>
       </c>
@@ -9889,16 +9847,16 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="10:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="10:12" x14ac:dyDescent="0.4">
       <c r="J53" s="1">
         <v>5.75</v>
       </c>
       <c r="K53" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L53" s="1">
         <f>J53*K53</f>
-        <v>80.5</v>
+        <v>86.25</v>
       </c>
     </row>
   </sheetData>
@@ -9919,20 +9877,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DAB656-BAD9-41F3-BF3B-171A85BDC607}">
   <dimension ref="A3:L28"/>
-  <sheetFormatPr defaultColWidth="22.8671875" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.25390625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.96484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.41015625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.6796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.48046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6015625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="22.8671875" style="2"/>
+    <col min="1" max="1" width="21.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="22.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" ht="35.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" ht="39" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>211</v>
       </c>
@@ -9944,7 +9902,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="5" spans="1:9" s="7" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="7" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
@@ -9964,7 +9922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="43">
         <v>46109</v>
       </c>
@@ -9988,7 +9946,7 @@
       </c>
       <c r="I6" s="52"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="43">
         <v>46161</v>
       </c>
@@ -10012,7 +9970,7 @@
       </c>
       <c r="I7" s="53"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="47">
         <v>46161</v>
       </c>
@@ -10032,7 +9990,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="61"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -10044,14 +10002,14 @@
       </c>
       <c r="I9" s="52"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="61"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="E10" s="1"/>
       <c r="F10" s="62"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="61"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -10059,14 +10017,14 @@
       <c r="E11" s="1"/>
       <c r="F11" s="62"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="61"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="E12" s="1"/>
       <c r="F12" s="62"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="61"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -10074,7 +10032,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="62"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="61"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -10082,14 +10040,14 @@
       <c r="E14" s="1"/>
       <c r="F14" s="62"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="61"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="E15" s="1"/>
       <c r="F15" s="62"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="61"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -10097,14 +10055,14 @@
       <c r="E16" s="1"/>
       <c r="F16" s="62"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="61"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="E17" s="1"/>
       <c r="F17" s="62"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="15"/>
       <c r="B18" s="1"/>
       <c r="C18" s="32"/>
@@ -10112,7 +10070,7 @@
       <c r="E18" s="33"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="31"/>
       <c r="B19" s="32"/>
       <c r="C19" s="32"/>
@@ -10120,14 +10078,14 @@
       <c r="E19" s="33"/>
       <c r="F19" s="35"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J20" s="94" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J20" s="88" t="s">
         <v>167</v>
       </c>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="F21" s="9" t="s">
         <v>150</v>
       </c>
@@ -10145,7 +10103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J22" s="1">
         <v>289.75</v>
       </c>
@@ -10157,18 +10115,18 @@
         <v>8113</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="K25" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J26" s="54"/>
       <c r="K26" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="K28" s="2">
         <f>SUM(K25:K27)</f>
         <v>29</v>
@@ -10190,18 +10148,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A010896-0EE6-4EC7-A4AB-4825B771304C}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A3:F10"/>
-  <sheetFormatPr defaultColWidth="22.8671875" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="24.2109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.0859375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1015625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.73828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="22.8671875" style="2"/>
+    <col min="4" max="4" width="29.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="22.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="37.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" ht="39" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>40</v>
       </c>
@@ -10211,7 +10169,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
-    <row r="5" spans="1:6" s="7" customFormat="1" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" s="7" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
@@ -10231,7 +10189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="15">
         <v>46019</v>
       </c>
@@ -10249,7 +10207,7 @@
       </c>
       <c r="F6" s="16"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="31">
         <v>46023</v>
       </c>
@@ -10267,7 +10225,7 @@
       </c>
       <c r="F7" s="35"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="31">
         <v>46023</v>
       </c>
@@ -10285,7 +10243,7 @@
       </c>
       <c r="F8" s="35"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="D10" s="9" t="s">
         <v>42</v>
       </c>
@@ -10307,22 +10265,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9294D21F-2AAF-4B66-B245-846FC5CB913E}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A3:C12"/>
-  <sheetFormatPr defaultColWidth="22.8671875" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.8671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.02734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.34765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="22.8671875" style="2"/>
+    <col min="1" max="1" width="22.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="22.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" ht="37.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:3" ht="39" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
     </row>
-    <row r="5" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>1</v>
       </c>
@@ -10333,7 +10291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="37.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A6" s="11">
         <v>46018</v>
       </c>
@@ -10342,32 +10300,32 @@
       </c>
       <c r="C6" s="14"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="11"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="11"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="11"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="11"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="11"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="4"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -10382,20 +10340,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0E0B56-B3D8-4E6A-AD96-8B588542D1E8}">
   <dimension ref="A3:L44"/>
-  <sheetFormatPr defaultColWidth="22.8671875" defaultRowHeight="21" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="22.88671875" defaultRowHeight="19.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.25390625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.96484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.41015625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.96484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.48046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.484375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.6015625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="22.8671875" style="2"/>
+    <col min="1" max="1" width="21.21875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="22.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" ht="37.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:9" ht="39" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>260</v>
       </c>
@@ -10407,7 +10365,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="5" spans="1:9" s="7" customFormat="1" ht="36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="7" customFormat="1" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>1</v>
       </c>
@@ -10427,7 +10385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="43">
         <v>46109</v>
       </c>
@@ -10451,7 +10409,7 @@
       </c>
       <c r="I6" s="52"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="61"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -10462,14 +10420,14 @@
       </c>
       <c r="I7" s="53"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="61"/>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="E8" s="1"/>
       <c r="F8" s="62"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="61"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -10481,14 +10439,14 @@
       </c>
       <c r="I9" s="52"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="61"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="E10" s="1"/>
       <c r="F10" s="62"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="61"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -10496,14 +10454,14 @@
       <c r="E11" s="1"/>
       <c r="F11" s="62"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="61"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
       <c r="E12" s="1"/>
       <c r="F12" s="62"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="61"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -10511,7 +10469,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="62"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="61"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -10519,14 +10477,14 @@
       <c r="E14" s="1"/>
       <c r="F14" s="62"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="61"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
       <c r="E15" s="1"/>
       <c r="F15" s="62"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="61"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -10534,14 +10492,14 @@
       <c r="E16" s="1"/>
       <c r="F16" s="62"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="61"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
       <c r="E17" s="1"/>
       <c r="F17" s="62"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="15"/>
       <c r="B18" s="1"/>
       <c r="C18" s="32"/>
@@ -10549,7 +10507,7 @@
       <c r="E18" s="33"/>
       <c r="F18" s="16"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="31"/>
       <c r="B19" s="32"/>
       <c r="C19" s="32"/>
@@ -10557,14 +10515,14 @@
       <c r="E19" s="33"/>
       <c r="F19" s="35"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="J20" s="94" t="s">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J20" s="88" t="s">
         <v>167</v>
       </c>
-      <c r="K20" s="94"/>
-      <c r="L20" s="94"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K20" s="88"/>
+      <c r="L20" s="88"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="F21" s="9" t="s">
         <v>150</v>
       </c>
@@ -10582,7 +10540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J22" s="1">
         <v>289.75</v>
       </c>
@@ -10594,12 +10552,12 @@
         <v>8113</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="K25" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="35.25" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:12" ht="39" x14ac:dyDescent="0.4">
       <c r="A27" s="12" t="s">
         <v>167</v>
       </c>
@@ -10611,13 +10569,13 @@
       <c r="G27" s="13"/>
       <c r="H27" s="13"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="J29" s="54"/>
       <c r="K29" s="2">
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="39.6" x14ac:dyDescent="0.4">
       <c r="A30" s="17" t="s">
         <v>2</v>
       </c>
@@ -10637,7 +10595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" s="61" t="s">
         <v>261</v>
       </c>
@@ -10661,21 +10619,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" s="61"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="E32" s="1"/>
       <c r="F32" s="62"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="61"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="E33" s="1"/>
       <c r="F33" s="62"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="61"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -10683,14 +10641,14 @@
       <c r="E34" s="1"/>
       <c r="F34" s="62"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="61"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="E35" s="1"/>
       <c r="F35" s="62"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="61"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -10698,14 +10656,14 @@
       <c r="E36" s="1"/>
       <c r="F36" s="62"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="61"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="E37" s="1"/>
       <c r="F37" s="62"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="61"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -10713,7 +10671,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="62"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="61"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -10721,14 +10679,14 @@
       <c r="E39" s="1"/>
       <c r="F39" s="62"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="61"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
       <c r="E40" s="1"/>
       <c r="F40" s="62"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="61"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -10736,14 +10694,14 @@
       <c r="E41" s="1"/>
       <c r="F41" s="62"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="61"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
       <c r="E42" s="1"/>
       <c r="F42" s="62"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="61"/>
       <c r="B43" s="1"/>
       <c r="C43" s="32"/>
@@ -10751,7 +10709,7 @@
       <c r="E43" s="32"/>
       <c r="F43" s="62"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="78"/>
       <c r="B44" s="32"/>
       <c r="C44" s="32"/>
